--- a/ig/DM-JUILLET-2026/ValueSet-jdv-difficulte-cisis.xlsx
+++ b/ig/DM-JUILLET-2026/ValueSet-jdv-difficulte-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260420150251</t>
+    <t>20260716085853</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:02:51+01:00</t>
+    <t>2026-07-16T08:58:53+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,10 +111,10 @@
     <t>difficile</t>
   </si>
   <si>
-    <t>702370009</t>
-  </si>
-  <si>
-    <t>procédure impossible</t>
+    <t>1303248003</t>
+  </si>
+  <si>
+    <t>non éligible à une procédure</t>
   </si>
   <si>
     <t/>
